--- a/artfynd/A 25152-2024 artfynd.xlsx
+++ b/artfynd/A 25152-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131665</v>
+        <v>122131668</v>
       </c>
       <c r="B2" t="n">
-        <v>90763</v>
+        <v>90754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575677</v>
+        <v>575753</v>
       </c>
       <c r="R2" t="n">
-        <v>7107655</v>
+        <v>7107631</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131672</v>
+        <v>122131666</v>
       </c>
       <c r="B3" t="n">
-        <v>90741</v>
+        <v>78639</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575761</v>
+        <v>575762</v>
       </c>
       <c r="R3" t="n">
-        <v>7107616</v>
+        <v>7107605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131666</v>
+        <v>122131665</v>
       </c>
       <c r="B4" t="n">
-        <v>78632</v>
+        <v>90772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575762</v>
+        <v>575677</v>
       </c>
       <c r="R4" t="n">
-        <v>7107605</v>
+        <v>7107655</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +984,7 @@
         <v>122132168</v>
       </c>
       <c r="B5" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131668</v>
+        <v>122131672</v>
       </c>
       <c r="B6" t="n">
-        <v>90745</v>
+        <v>90750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575753</v>
+        <v>575761</v>
       </c>
       <c r="R6" t="n">
-        <v>7107631</v>
+        <v>7107616</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 25152-2024 artfynd.xlsx
+++ b/artfynd/A 25152-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131672</v>
+        <v>122131665</v>
       </c>
       <c r="B2" t="n">
-        <v>90775</v>
+        <v>90797</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575761</v>
+        <v>575677</v>
       </c>
       <c r="R2" t="n">
-        <v>7107616</v>
+        <v>7107655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131668</v>
+        <v>122132168</v>
       </c>
       <c r="B3" t="n">
-        <v>90779</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575753</v>
+        <v>575670</v>
       </c>
       <c r="R3" t="n">
-        <v>7107631</v>
+        <v>7107654</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131665</v>
+        <v>122131668</v>
       </c>
       <c r="B4" t="n">
-        <v>90797</v>
+        <v>90779</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575677</v>
+        <v>575753</v>
       </c>
       <c r="R4" t="n">
-        <v>7107655</v>
+        <v>7107631</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131666</v>
+        <v>122131672</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>90775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575762</v>
+        <v>575761</v>
       </c>
       <c r="R5" t="n">
-        <v>7107605</v>
+        <v>7107616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122132168</v>
+        <v>122131666</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>78645</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575670</v>
+        <v>575762</v>
       </c>
       <c r="R6" t="n">
-        <v>7107654</v>
+        <v>7107605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 25152-2024 artfynd.xlsx
+++ b/artfynd/A 25152-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131665</v>
+        <v>122131668</v>
       </c>
       <c r="B2" t="n">
-        <v>90797</v>
+        <v>90789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575677</v>
+        <v>575753</v>
       </c>
       <c r="R2" t="n">
-        <v>7107655</v>
+        <v>7107631</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122132168</v>
+        <v>122131665</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>90807</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575670</v>
+        <v>575677</v>
       </c>
       <c r="R3" t="n">
-        <v>7107654</v>
+        <v>7107655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131668</v>
+        <v>122131672</v>
       </c>
       <c r="B4" t="n">
-        <v>90779</v>
+        <v>90785</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575753</v>
+        <v>575761</v>
       </c>
       <c r="R4" t="n">
-        <v>7107631</v>
+        <v>7107616</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131672</v>
+        <v>122131666</v>
       </c>
       <c r="B5" t="n">
-        <v>90775</v>
+        <v>78646</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575761</v>
+        <v>575762</v>
       </c>
       <c r="R5" t="n">
-        <v>7107616</v>
+        <v>7107605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131666</v>
+        <v>122132168</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575762</v>
+        <v>575670</v>
       </c>
       <c r="R6" t="n">
-        <v>7107605</v>
+        <v>7107654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 25152-2024 artfynd.xlsx
+++ b/artfynd/A 25152-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131668</v>
+        <v>122132168</v>
       </c>
       <c r="B2" t="n">
-        <v>90789</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575753</v>
+        <v>575670</v>
       </c>
       <c r="R2" t="n">
-        <v>7107631</v>
+        <v>7107654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131666</v>
+        <v>122131668</v>
       </c>
       <c r="B5" t="n">
-        <v>78646</v>
+        <v>90789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575762</v>
+        <v>575753</v>
       </c>
       <c r="R5" t="n">
-        <v>7107605</v>
+        <v>7107631</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122132168</v>
+        <v>122131666</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575670</v>
+        <v>575762</v>
       </c>
       <c r="R6" t="n">
-        <v>7107654</v>
+        <v>7107605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 25152-2024 artfynd.xlsx
+++ b/artfynd/A 25152-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122132168</v>
+        <v>122131672</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>90797</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575670</v>
+        <v>575761</v>
       </c>
       <c r="R2" t="n">
-        <v>7107654</v>
+        <v>7107616</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131665</v>
+        <v>122131668</v>
       </c>
       <c r="B3" t="n">
-        <v>90807</v>
+        <v>90801</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575677</v>
+        <v>575753</v>
       </c>
       <c r="R3" t="n">
-        <v>7107655</v>
+        <v>7107631</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131672</v>
+        <v>122132168</v>
       </c>
       <c r="B4" t="n">
-        <v>90785</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575761</v>
+        <v>575670</v>
       </c>
       <c r="R4" t="n">
-        <v>7107616</v>
+        <v>7107654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131668</v>
+        <v>122131665</v>
       </c>
       <c r="B5" t="n">
-        <v>90789</v>
+        <v>90819</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575753</v>
+        <v>575677</v>
       </c>
       <c r="R5" t="n">
-        <v>7107631</v>
+        <v>7107655</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
         <v>122131666</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 25152-2024 artfynd.xlsx
+++ b/artfynd/A 25152-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131672</v>
+        <v>122131666</v>
       </c>
       <c r="B2" t="n">
-        <v>90797</v>
+        <v>78651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575761</v>
+        <v>575762</v>
       </c>
       <c r="R2" t="n">
-        <v>7107616</v>
+        <v>7107605</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131668</v>
+        <v>122131665</v>
       </c>
       <c r="B3" t="n">
-        <v>90801</v>
+        <v>90826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575753</v>
+        <v>575677</v>
       </c>
       <c r="R3" t="n">
-        <v>7107631</v>
+        <v>7107655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132168</v>
+        <v>122131668</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>90808</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575670</v>
+        <v>575753</v>
       </c>
       <c r="R4" t="n">
-        <v>7107654</v>
+        <v>7107631</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131665</v>
+        <v>122131672</v>
       </c>
       <c r="B5" t="n">
-        <v>90819</v>
+        <v>90804</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575677</v>
+        <v>575761</v>
       </c>
       <c r="R5" t="n">
-        <v>7107655</v>
+        <v>7107616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131666</v>
+        <v>122132168</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575762</v>
+        <v>575670</v>
       </c>
       <c r="R6" t="n">
-        <v>7107605</v>
+        <v>7107654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 25152-2024 artfynd.xlsx
+++ b/artfynd/A 25152-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131666</v>
+        <v>122131668</v>
       </c>
       <c r="B2" t="n">
-        <v>78651</v>
+        <v>90813</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575762</v>
+        <v>575753</v>
       </c>
       <c r="R2" t="n">
-        <v>7107605</v>
+        <v>7107631</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +775,7 @@
         <v>122131665</v>
       </c>
       <c r="B3" t="n">
-        <v>90826</v>
+        <v>90831</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,11 +789,6 @@
       </c>
       <c r="E3" t="n">
         <v>5432</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131668</v>
+        <v>122132168</v>
       </c>
       <c r="B4" t="n">
-        <v>90808</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +885,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575753</v>
+        <v>575670</v>
       </c>
       <c r="R4" t="n">
-        <v>7107631</v>
+        <v>7107654</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131672</v>
+        <v>122131666</v>
       </c>
       <c r="B5" t="n">
-        <v>90804</v>
+        <v>78652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +982,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575761</v>
+        <v>575762</v>
       </c>
       <c r="R5" t="n">
-        <v>7107616</v>
+        <v>7107605</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122132168</v>
+        <v>122131672</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>90809</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1079,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1108</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575670</v>
+        <v>575761</v>
       </c>
       <c r="R6" t="n">
-        <v>7107654</v>
+        <v>7107616</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 25152-2024 artfynd.xlsx
+++ b/artfynd/A 25152-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122131668</v>
       </c>
       <c r="B2" t="n">
-        <v>90813</v>
+        <v>90826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>1202</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131665</v>
+        <v>122131666</v>
       </c>
       <c r="B3" t="n">
-        <v>90831</v>
+        <v>78656</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -788,16 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575677</v>
+        <v>575762</v>
       </c>
       <c r="R3" t="n">
-        <v>7107655</v>
+        <v>7107605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122132168</v>
+        <v>122131672</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>90822</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -885,16 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1108</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575670</v>
+        <v>575761</v>
       </c>
       <c r="R4" t="n">
-        <v>7107654</v>
+        <v>7107616</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131666</v>
+        <v>122131665</v>
       </c>
       <c r="B5" t="n">
-        <v>78652</v>
+        <v>90844</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -982,16 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575762</v>
+        <v>575677</v>
       </c>
       <c r="R5" t="n">
-        <v>7107605</v>
+        <v>7107655</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131672</v>
+        <v>122132168</v>
       </c>
       <c r="B6" t="n">
-        <v>90809</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1079,16 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575761</v>
+        <v>575670</v>
       </c>
       <c r="R6" t="n">
-        <v>7107616</v>
+        <v>7107654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 25152-2024 artfynd.xlsx
+++ b/artfynd/A 25152-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131668</v>
+        <v>122132168</v>
       </c>
       <c r="B2" t="n">
-        <v>90826</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575753</v>
+        <v>575670</v>
       </c>
       <c r="R2" t="n">
-        <v>7107631</v>
+        <v>7107654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131666</v>
+        <v>122131668</v>
       </c>
       <c r="B3" t="n">
-        <v>78656</v>
+        <v>90839</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575762</v>
+        <v>575753</v>
       </c>
       <c r="R3" t="n">
-        <v>7107605</v>
+        <v>7107631</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131672</v>
+        <v>122131665</v>
       </c>
       <c r="B4" t="n">
-        <v>90822</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575761</v>
+        <v>575677</v>
       </c>
       <c r="R4" t="n">
-        <v>7107616</v>
+        <v>7107655</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131665</v>
+        <v>122131672</v>
       </c>
       <c r="B5" t="n">
-        <v>90844</v>
+        <v>90835</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575677</v>
+        <v>575761</v>
       </c>
       <c r="R5" t="n">
-        <v>7107655</v>
+        <v>7107616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122132168</v>
+        <v>122131666</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575670</v>
+        <v>575762</v>
       </c>
       <c r="R6" t="n">
-        <v>7107654</v>
+        <v>7107605</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
